--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,106 +448,190 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61702</v>
+        <v>34067</v>
       </c>
       <c r="C2" t="n">
-        <v>61697</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>61702</v>
-      </c>
+        <v>34067</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+34067</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>50810</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
+        <v>50810</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+50810</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19976</v>
+        <v>76503</v>
       </c>
       <c r="C4" t="n">
-        <v>19976</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+        <v>76498</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+14801</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>19976</v>
+        <v>61702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6199</v>
+        <v>77665</v>
       </c>
       <c r="C5" t="n">
-        <v>6172</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+        <v>77664</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+77663</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>6199</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87879</v>
+        <v>21718</v>
       </c>
       <c r="C6" t="n">
-        <v>87847</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>21718</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+21718</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>25132</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+5156</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19976</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>（未匹配门店）</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>29746</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29744</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+29746</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>未消费会员</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14378</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14285</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+8179</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6199</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>330019</v>
+      </c>
+      <c r="C10" t="n">
+        <v>329918</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B11" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -560,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +657,436 @@
         <is>
           <t>记录数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>（旧）DJI北京西红门荟聚中心授权体验店</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7678</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>（旧）DJI北京王府井APM授权高级体验店</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>（旧）DJI大疆哈苏北京华熙LIVE概念店</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>APR贵阳亨特广场（已闭店）</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>APR上海天空万科广场（已闭店）</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>APR重庆时代天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>APR郑州正弘汇（已闭店）</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>APR郑州荥阳吾悦（已闭店）</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>APR贵阳南国花锦（已闭店）</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APR贵阳金阳国贸（已闭店）</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APR上海前滩太古里（已闭店）</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>APR重庆高新天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>（旧）-APR成都凯德魅力城</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>APR重庆U城天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APR贵阳花果园（已闭店）</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>APR重庆金沙天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>APR郑州探十里（已闭店）</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>APR上海宝山天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>APR重庆南坪协信（已闭店）</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>APR昆明七彩云南（已闭店）</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>APR重庆江岸天街（已闭店）</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>APR郑州国贸 360（已闭店）</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>APR贵阳万科广场（已闭店）</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>APR昆明同德广场（已闭店）</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>APR上海宝杨宝龙广场（已闭店）</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>APR上海静安大融城（已闭店）</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>APR重庆东原悦荟（已闭店）</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>APP上海虹桥前湾印象城（已闭店）</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>APR上海虹口凯德（已闭店）</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>APR上海荟聚中心（已闭店）</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>APR郑州金水印象汇（已闭店）</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>APR重庆桃源天地（已闭店）</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>APR上海陆悦天地（已闭店）</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>华为福州福清高山（已闭店）</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>APR上海天空之城ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>华为北京常营龙湖（已闭店）</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>APR上海三林印象汇（已闭店）</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>APR昆明七彩云南ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>APR上海前湾印象城ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>APR上海唐镇印象汇（已闭店）</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APR昆明万象城（已闭店）</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APR昆明同德广场ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APR贵阳亨特广场ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -586,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,16 +1128,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖</t>
+          <t>DJI上海嘉亭荟授权体验店</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -632,16 +1146,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>DJI上海FFC滨江悦里授权体验店</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>322</v>
+        <v>171</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -650,16 +1164,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>DJI上海百联青浦奥莱授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>372</v>
+        <v>192</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -668,16 +1182,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -686,16 +1200,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>DJI大疆哈苏上海新嘉中心概念店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>493</v>
+        <v>389</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -704,16 +1218,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>AAR北京五棵松店</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -722,16 +1236,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>APR北京昌发展万科</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>568</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -740,90 +1254,414 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华为宁德霞浦太康路一店</t>
+          <t>APR北京大红门银泰</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>584</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华为宁德霞浦太康路二店</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>594</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>华为宁德古田中央名城</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>668</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>华为厦门思明星河COCO Park</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63</v>
+        <v>410</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>华为北京京投小站</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>464</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华为北京上德银泰</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>623</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>华为北京房山燕隆汇</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>643</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>华为北京同成街华联</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>661</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DJI大疆北京西直门凯德mall授权体验店</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>159</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DJI北京双安商场授权体验店</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>237</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DJI北京北投新奥天虹授权体验店</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>631</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DJI北京万柳华联授权体验店</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>648</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>北京飞航</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DJI北京龙湖长安天街授权体验店</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>766</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>（旧）APR成都凯德魅力城</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>133</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>（旧）APR成都东安天街</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>238</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>APR成都新光天地</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>290</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>（旧）APR成都环球中心</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>295</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>四川新跃</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>（旧）APR成都天府环宇坊</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>341</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>福建易联</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>华为宁德霞浦方圆荟</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>71</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦太康路一店</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦太康路二店</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>88</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>华为厦门思明星河COCO Park</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>111</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>华为厦门湖里江头</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>144</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>华为厦门思明大西洋天虹</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>231</v>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
     </row>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,17 +452,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+87</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34067</v>
       </c>
-      <c r="C2" t="n">
-        <v>34067</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+34067</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,17 +473,19 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>51132</v>
+      </c>
+      <c r="C3" t="n">
+        <v>51132</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+322</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>50810</v>
       </c>
-      <c r="C3" t="n">
-        <v>50810</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+50810</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -490,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>76729</v>
+      </c>
+      <c r="C4" t="n">
+        <v>76724</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+226</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>76503</v>
-      </c>
-      <c r="C4" t="n">
-        <v>76498</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+14801</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>61702</v>
       </c>
     </row>
     <row r="5">
@@ -511,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93243</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93242</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+15578</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>77665</v>
-      </c>
-      <c r="C5" t="n">
-        <v>77664</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+77663</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -532,17 +536,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>21865</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21865</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+147</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>21718</v>
       </c>
-      <c r="C6" t="n">
-        <v>21718</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+21718</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -551,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25227</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25227</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+95</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25132</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25132</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+5156</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>19976</v>
       </c>
     </row>
     <row r="8">
@@ -572,17 +578,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14347</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14346</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-15399</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>29746</v>
       </c>
-      <c r="C8" t="n">
-        <v>29744</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+29746</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -591,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14396</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14302</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14378</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14285</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+8179</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6199</v>
       </c>
     </row>
     <row r="10">
@@ -612,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>330019</v>
+        <v>331093</v>
       </c>
       <c r="C10" t="n">
-        <v>329918</v>
+        <v>330992</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -644,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,430 +670,400 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（旧）DJI北京西红门荟聚中心授权体验店</t>
+          <t>APR贵阳亨特广场（已闭店）</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7678</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>（旧）DJI北京王府井APM授权高级体验店</t>
+          <t>APR上海天空万科广场（已闭店）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5253</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>（旧）DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>APR重庆时代天街（已闭店）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2468</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APR贵阳亨特广场（已闭店）</t>
+          <t>APR郑州正弘汇（已闭店）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>835</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APR上海天空万科广场（已闭店）</t>
+          <t>APR郑州荥阳吾悦（已闭店）</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>657</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APR重庆时代天街（已闭店）</t>
+          <t>APR贵阳南国花锦（已闭店）</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APR郑州正弘汇（已闭店）</t>
+          <t>APR贵阳金阳国贸（已闭店）</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>603</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APR郑州荥阳吾悦（已闭店）</t>
+          <t>APR上海前滩太古里（已闭店）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>580</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APR贵阳南国花锦（已闭店）</t>
+          <t>APR重庆高新天街（已闭店）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APR贵阳金阳国贸（已闭店）</t>
+          <t>（旧）-APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>546</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APR上海前滩太古里（已闭店）</t>
+          <t>APR重庆U城天街（已闭店）</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>541</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APR重庆高新天街（已闭店）</t>
+          <t>APR贵阳花果园（已闭店）</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>521</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>（旧）-APR成都凯德魅力城</t>
+          <t>APR重庆金沙天街（已闭店）</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>500</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APR重庆U城天街（已闭店）</t>
+          <t>APR郑州探十里（已闭店）</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APR贵阳花果园（已闭店）</t>
+          <t>APR上海宝山天街（已闭店）</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>484</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APR重庆金沙天街（已闭店）</t>
+          <t>APR重庆南坪协信（已闭店）</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>476</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APR郑州探十里（已闭店）</t>
+          <t>APR昆明七彩云南（已闭店）</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>471</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APR上海宝山天街（已闭店）</t>
+          <t>APR重庆江岸天街（已闭店）</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APR重庆南坪协信（已闭店）</t>
+          <t>APR郑州国贸 360（已闭店）</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>APR昆明七彩云南（已闭店）</t>
+          <t>APR贵阳万科广场（已闭店）</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>415</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APR重庆江岸天街（已闭店）</t>
+          <t>APR昆明同德广场（已闭店）</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>414</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>APR郑州国贸 360（已闭店）</t>
+          <t>APR上海宝杨宝龙广场（已闭店）</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>406</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>APR贵阳万科广场（已闭店）</t>
+          <t>APR上海静安大融城（已闭店）</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>387</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APR昆明同德广场（已闭店）</t>
+          <t>APR重庆东原悦荟（已闭店）</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>381</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>APR上海宝杨宝龙广场（已闭店）</t>
+          <t>APP上海虹桥前湾印象城（已闭店）</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>APR上海静安大融城（已闭店）</t>
+          <t>APR上海虹口凯德（已闭店）</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>APR重庆东原悦荟（已闭店）</t>
+          <t>APR上海荟聚中心（已闭店）</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>344</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>APP上海虹桥前湾印象城（已闭店）</t>
+          <t>APR郑州金水印象汇（已闭店）</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>340</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>APR上海虹口凯德（已闭店）</t>
+          <t>APR重庆桃源天地（已闭店）</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>328</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>APR上海荟聚中心（已闭店）</t>
+          <t>APR上海陆悦天地（已闭店）</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>321</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>APR郑州金水印象汇（已闭店）</t>
+          <t>华为福州福清高山（已闭店）</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>298</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APR重庆桃源天地（已闭店）</t>
+          <t>APR上海天空之城ASP（已闭店）</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>272</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>APR上海陆悦天地（已闭店）</t>
+          <t>华为北京常营龙湖（已闭店）</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>华为福州福清高山（已闭店）</t>
+          <t>APR上海三林印象汇（已闭店）</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>APR上海天空之城ASP（已闭店）</t>
+          <t>APR昆明七彩云南ASP（已闭店）</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖（已闭店）</t>
+          <t>APR上海前湾印象城ASP（已闭店）</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>111</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>APR上海三林印象汇（已闭店）</t>
+          <t>APR上海唐镇印象汇（已闭店）</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>111</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APR昆明七彩云南ASP（已闭店）</t>
+          <t>APR昆明万象城（已闭店）</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APR上海前湾印象城ASP（已闭店）</t>
+          <t>APR昆明同德广场ASP（已闭店）</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APR上海唐镇印象汇（已闭店）</t>
+          <t>APR贵阳亨特广场ASP（已闭店）</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>APR昆明万象城（已闭店）</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>APR昆明同德广场ASP（已闭店）</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>APR贵阳亨特广场ASP（已闭店）</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1137,7 +1115,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1173,7 +1151,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1191,7 +1169,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1209,7 +1187,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1245,7 +1223,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1263,7 +1241,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1281,7 +1259,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1299,7 +1277,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1317,7 +1295,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1335,7 +1313,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1371,7 +1349,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1389,7 +1367,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1403,11 +1381,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI大疆北京西直门凯德mall授权体验店</t>
+          <t>DJI北京王府井APM授权高级体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1421,11 +1399,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京双安商场授权体验店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>237</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1439,11 +1417,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>631</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1457,11 +1435,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI大疆北京西直门凯德mall授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>648</v>
+        <v>162</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1475,11 +1453,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>766</v>
+        <v>239</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1493,11 +1471,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>（旧）APR成都凯德魅力城</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1511,11 +1489,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>（旧）APR成都东安天街</t>
+          <t>（旧）APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>238</v>
+        <v>133</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1529,11 +1507,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>APR成都新光天地</t>
+          <t>（旧）APR成都东安天街</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1565,11 +1543,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>（旧）APR成都天府环宇坊</t>
+          <t>APR成都新光天地</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1605,7 +1583,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34253</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34253</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+99</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34154</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+87</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34067</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>51403</v>
+      </c>
+      <c r="C3" t="n">
+        <v>51403</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+271</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>51132</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51132</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+322</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>50810</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>76948</v>
+      </c>
+      <c r="C4" t="n">
+        <v>76943</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+219</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>76729</v>
-      </c>
-      <c r="C4" t="n">
-        <v>76724</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+226</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>76503</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93421</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93420</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+178</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>93243</v>
-      </c>
-      <c r="C5" t="n">
-        <v>93242</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+15578</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>77665</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>21982</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+117</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>21865</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21865</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+147</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>21718</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25308</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25308</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+81</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25227</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25227</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+95</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25132</v>
       </c>
     </row>
     <row r="8">
@@ -583,13 +583,11 @@
       <c r="C8" t="n">
         <v>14346</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-15399</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>29746</v>
+        <v>14347</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +597,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14414</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14320</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14396</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14302</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+18</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14378</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +618,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>331093</v>
+        <v>332076</v>
       </c>
       <c r="C10" t="n">
-        <v>330992</v>
+        <v>331975</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1115,7 +1113,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1133,7 +1131,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1151,7 +1149,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1169,7 +1167,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1187,7 +1185,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1205,7 +1203,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1223,7 +1221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1241,7 +1239,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1277,7 +1275,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1295,7 +1293,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1313,7 +1311,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1331,7 +1329,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1349,7 +1347,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1367,7 +1365,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1385,7 +1383,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1399,11 +1397,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1417,11 +1415,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1439,7 +1437,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1457,7 +1455,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1475,7 +1473,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1547,7 +1545,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1583,7 +1581,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34333</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+80</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34253</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34253</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+99</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34154</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>51812</v>
+      </c>
+      <c r="C3" t="n">
+        <v>51812</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+409</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>51403</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51403</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+271</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>51132</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>77196</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77191</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+248</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>76948</v>
-      </c>
-      <c r="C4" t="n">
-        <v>76943</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+219</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>76729</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93644</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93643</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+223</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>93421</v>
-      </c>
-      <c r="C5" t="n">
-        <v>93420</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+178</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>93243</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>22148</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22148</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+166</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>21982</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21982</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+117</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>21865</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25401</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25401</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+93</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25308</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25308</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+81</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25227</v>
       </c>
     </row>
     <row r="8">
@@ -597,18 +597,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14438</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14343</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+24</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14414</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14320</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+18</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14396</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>332076</v>
+        <v>333319</v>
       </c>
       <c r="C10" t="n">
-        <v>331975</v>
+        <v>333217</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -758,7 +758,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>（旧）-APR成都凯德魅力城</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI北京王府井APM授权高级体验店</t>
+          <t>DJI大疆北京西直门凯德mall授权体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1397,11 +1397,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>242</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1415,11 +1415,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>641</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI大疆北京西直门凯德mall授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>167</v>
+        <v>650</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI北京双安商场授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>240</v>
+        <v>778</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1487,11 +1487,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>（旧）APR成都凯德魅力城</t>
+          <t>APR成都新光天地</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>133</v>
+        <v>304</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1505,11 +1505,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>（旧）APR成都东安天街</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>238</v>
+        <v>668</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>（旧）APR成都环球中心</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>295</v>
+        <v>753</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1541,11 +1541,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APR成都新光天地</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>299</v>
+        <v>756</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34486</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34486</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+153</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34333</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34333</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+80</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34253</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>52399</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52399</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+587</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>51812</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51812</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+409</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>51403</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>77611</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77606</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+415</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>77196</v>
-      </c>
-      <c r="C4" t="n">
-        <v>77191</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+248</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>76948</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93961</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93960</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+317</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>93644</v>
-      </c>
-      <c r="C5" t="n">
-        <v>93643</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+223</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>93421</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>22443</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22443</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+295</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>22148</v>
-      </c>
-      <c r="C6" t="n">
-        <v>22148</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+166</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>21982</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25549</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25549</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+148</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25401</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25401</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+93</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25308</v>
       </c>
     </row>
     <row r="8">
@@ -597,18 +597,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14485</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14390</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+47</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14438</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14343</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+24</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14414</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>333319</v>
+        <v>335281</v>
       </c>
       <c r="C10" t="n">
-        <v>333217</v>
+        <v>335179</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34688</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34688</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+202</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34486</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34486</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+153</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34333</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>52888</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52888</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+489</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>52399</v>
-      </c>
-      <c r="C3" t="n">
-        <v>52399</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+587</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>51812</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>77986</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77981</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+375</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>77611</v>
-      </c>
-      <c r="C4" t="n">
-        <v>77606</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+415</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>77196</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>94215</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94214</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+254</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>93961</v>
-      </c>
-      <c r="C5" t="n">
-        <v>93960</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+317</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>93644</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>22686</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22686</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+243</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>22443</v>
-      </c>
-      <c r="C6" t="n">
-        <v>22443</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+295</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>22148</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25699</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25699</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25549</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25549</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+148</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25401</v>
       </c>
     </row>
     <row r="8">
@@ -578,13 +578,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14347</v>
+        <v>14357</v>
       </c>
       <c r="C8" t="n">
-        <v>14346</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
+        <v>14356</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>14347</v>
@@ -597,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14530</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14435</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+45</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14485</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14390</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+47</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14438</v>
       </c>
     </row>
     <row r="10">
@@ -618,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>335281</v>
+        <v>337049</v>
       </c>
       <c r="C10" t="n">
-        <v>335179</v>
+        <v>336947</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -650,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,10 +1060,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>华为福州东二环泰禾广场</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>APR贵阳亨特广场ASP（已闭店）</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1113,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1131,7 +1143,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1149,7 +1161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1167,7 +1179,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1185,7 +1197,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1203,7 +1215,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1221,7 +1233,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1239,7 +1251,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1257,7 +1269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1275,7 +1287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1293,7 +1305,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1329,7 +1341,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1347,7 +1359,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1365,7 +1377,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1383,7 +1395,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1419,7 +1431,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1437,7 +1449,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1455,7 +1467,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1473,7 +1485,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1491,7 +1503,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1509,7 +1521,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1527,7 +1539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1541,11 +1553,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>APR成都武侯吾悦</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1563,7 +1575,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1581,7 +1593,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1635,7 +1647,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34764</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34764</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+76</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34688</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34688</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+202</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34486</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>53199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53199</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>52888</v>
-      </c>
-      <c r="C3" t="n">
-        <v>52888</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+489</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>52399</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>78217</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78212</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+231</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>77986</v>
-      </c>
-      <c r="C4" t="n">
-        <v>77981</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+375</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>77611</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>94379</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94378</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+164</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>94215</v>
-      </c>
-      <c r="C5" t="n">
-        <v>94214</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+254</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>93961</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>22838</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22838</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+152</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>22686</v>
-      </c>
-      <c r="C6" t="n">
-        <v>22686</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+243</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>22443</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25798</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25798</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+99</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25699</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25699</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+150</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25549</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14363</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14362</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>14357</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14356</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+10</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14347</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14542</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14448</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14530</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14435</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+45</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14485</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>337049</v>
+        <v>338100</v>
       </c>
       <c r="C10" t="n">
-        <v>336947</v>
+        <v>337999</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34764</v>
+        <v>34832</v>
       </c>
       <c r="C2" t="n">
-        <v>34764</v>
+        <v>34832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+76</t>
+          <t>+144</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53199</v>
+        <v>53495</v>
       </c>
       <c r="C3" t="n">
-        <v>53199</v>
+        <v>53495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+311</t>
+          <t>+607</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>78217</v>
+        <v>78421</v>
       </c>
       <c r="C4" t="n">
-        <v>78212</v>
+        <v>78416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+231</t>
+          <t>+435</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94379</v>
+        <v>94531</v>
       </c>
       <c r="C5" t="n">
-        <v>94378</v>
+        <v>94530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+164</t>
+          <t>+316</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22838</v>
+        <v>22960</v>
       </c>
       <c r="C6" t="n">
-        <v>22838</v>
+        <v>22960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+152</t>
+          <t>+274</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25798</v>
+        <v>25892</v>
       </c>
       <c r="C7" t="n">
-        <v>25798</v>
+        <v>25892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+99</t>
+          <t>+193</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14363</v>
+        <v>14371</v>
       </c>
       <c r="C8" t="n">
-        <v>14362</v>
+        <v>14370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,14 +599,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14542</v>
+        <v>14574</v>
       </c>
       <c r="C9" t="n">
-        <v>14448</v>
+        <v>14482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+12</t>
+          <t>+44</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>338100</v>
+        <v>339076</v>
       </c>
       <c r="C10" t="n">
-        <v>337999</v>
+        <v>338977</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34907</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34907</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+75</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34832</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34832</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+144</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34688</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>53738</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53738</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+243</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>53495</v>
-      </c>
-      <c r="C3" t="n">
-        <v>53495</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+607</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>52888</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>78690</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+269</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>78421</v>
-      </c>
-      <c r="C4" t="n">
-        <v>78416</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+435</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>77986</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>94703</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94702</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+172</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>94531</v>
-      </c>
-      <c r="C5" t="n">
-        <v>94530</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+316</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>94215</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>23090</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23090</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>22960</v>
-      </c>
-      <c r="C6" t="n">
-        <v>22960</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+274</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>22686</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>25975</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+83</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25892</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25892</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+193</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25699</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14379</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14378</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>14371</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14370</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14357</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14609</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14513</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+35</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14574</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14482</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+44</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14530</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>339076</v>
+        <v>340091</v>
       </c>
       <c r="C10" t="n">
-        <v>338977</v>
+        <v>339988</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>

--- a/member_deposit/会员沉淀分析.xlsx
+++ b/member_deposit/会员沉淀分析.xlsx
@@ -452,18 +452,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>34993</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34993</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+86</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>34907</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34907</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+75</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>34832</v>
       </c>
     </row>
     <row r="3">
@@ -473,18 +473,18 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>54050</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54050</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+312</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>53738</v>
-      </c>
-      <c r="C3" t="n">
-        <v>53738</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+243</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>53495</v>
       </c>
     </row>
     <row r="4">
@@ -494,18 +494,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>78972</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+282</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>78690</v>
-      </c>
-      <c r="C4" t="n">
-        <v>78685</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+269</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>78421</v>
       </c>
     </row>
     <row r="5">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>94696</v>
+      </c>
+      <c r="C5" t="n">
+        <v>94695</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>94703</v>
-      </c>
-      <c r="C5" t="n">
-        <v>94702</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+172</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>94531</v>
       </c>
     </row>
     <row r="6">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>23242</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23242</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+152</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>23090</v>
-      </c>
-      <c r="C6" t="n">
-        <v>23090</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+130</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>22960</v>
       </c>
     </row>
     <row r="7">
@@ -557,18 +557,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>26062</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26062</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+87</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>25975</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25975</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+83</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25892</v>
       </c>
     </row>
     <row r="8">
@@ -578,18 +578,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14593</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14592</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+214</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>14379</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14378</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14371</v>
       </c>
     </row>
     <row r="9">
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14650</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14554</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+41</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>14609</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14513</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+35</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14574</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>340091</v>
+        <v>341258</v>
       </c>
       <c r="C10" t="n">
-        <v>339988</v>
+        <v>341155</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,37 +970,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>华为福州福清高山（已闭店）</t>
+          <t>DJI北京西直门凯德mall授权体验店</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>145</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APR上海天空之城ASP（已闭店）</t>
+          <t>华为福州福清高山（已闭店）</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖（已闭店）</t>
+          <t>APR上海天空之城ASP（已闭店）</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>APR上海三林印象汇（已闭店）</t>
+          <t>华为北京常营龙湖（已闭店）</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1010,51 +1010,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>APR昆明七彩云南ASP（已闭店）</t>
+          <t>APR上海三林印象汇（已闭店）</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>APR上海前湾印象城ASP（已闭店）</t>
+          <t>APR昆明七彩云南ASP（已闭店）</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>APR上海唐镇印象汇（已闭店）</t>
+          <t>APR上海前湾印象城ASP（已闭店）</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APR昆明万象城（已闭店）</t>
+          <t>APR上海唐镇印象汇（已闭店）</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APR昆明同德广场ASP（已闭店）</t>
+          <t>APR昆明万象城（已闭店）</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -1064,16 +1064,26 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>APR昆明同德广场ASP（已闭店）</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>APR贵阳亨特广场ASP（已闭店）</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B43" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1125,7 +1135,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1143,7 +1153,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1161,7 +1171,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1179,7 +1189,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1197,7 +1207,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1215,7 +1225,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1233,7 +1243,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1251,7 +1261,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1269,7 +1279,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -1287,7 +1297,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -1305,7 +1315,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1323,7 +1333,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1359,7 +1369,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -1377,7 +1387,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -1391,11 +1401,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DJI大疆北京西直门凯德mall授权体验店</t>
+          <t>DJI北京双安商场授权体验店</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1409,11 +1419,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI北京双安商场授权体验店</t>
+          <t>DJI北京北投新奥天虹授权体验店</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>247</v>
+        <v>652</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1427,11 +1437,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1445,11 +1455,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>658</v>
+        <v>807</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1463,11 +1473,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1485,7 +1495,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1503,7 +1513,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1521,7 +1531,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1539,7 +1549,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1557,7 +1567,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
